--- a/research/traditional_assets/database/data/jordan/jordan_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_chemical_basic.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.06758</v>
+        <v>-0.184</v>
       </c>
       <c r="G2">
-        <v>0.03406940063091482</v>
+        <v>-0.1922924116011124</v>
       </c>
       <c r="H2">
-        <v>0.03406940063091482</v>
+        <v>-0.1922924116011124</v>
       </c>
       <c r="I2">
-        <v>-0.3097791798107256</v>
+        <v>-0.3889551052840684</v>
       </c>
       <c r="J2">
-        <v>-0.3097791798107256</v>
+        <v>-0.3889551052840684</v>
       </c>
       <c r="K2">
-        <v>-1.364</v>
+        <v>-1.572</v>
       </c>
       <c r="L2">
-        <v>-0.4302839116719243</v>
+        <v>-0.6245530393325388</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.44</v>
+        <v>0.674</v>
       </c>
       <c r="V2">
-        <v>0.1164021164021164</v>
+        <v>0.2237715803452855</v>
       </c>
       <c r="W2">
-        <v>-0.1977139671922281</v>
+        <v>-0.359291145163177</v>
       </c>
       <c r="X2">
-        <v>0.441357062881005</v>
+        <v>0.4334268246672823</v>
       </c>
       <c r="Y2">
-        <v>-0.6390710300732331</v>
+        <v>-0.7927179698304593</v>
       </c>
       <c r="Z2">
-        <v>0.1554836178144006</v>
+        <v>0.1327041704012232</v>
       </c>
       <c r="AA2">
-        <v>-0.05250126986986269</v>
+        <v>-0.06158833789183905</v>
       </c>
       <c r="AB2">
-        <v>0.1856039210569446</v>
+        <v>0.1522651394467018</v>
       </c>
       <c r="AC2">
-        <v>-0.2381051909268073</v>
+        <v>-0.2138534773385408</v>
       </c>
       <c r="AD2">
-        <v>7.41</v>
+        <v>7.92</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.41</v>
+        <v>7.92</v>
       </c>
       <c r="AG2">
-        <v>6.97</v>
+        <v>7.246</v>
       </c>
       <c r="AH2">
-        <v>0.6621983914209114</v>
+        <v>0.7244785949506037</v>
       </c>
       <c r="AI2">
-        <v>0.3825503355704698</v>
+        <v>0.4335687304976186</v>
       </c>
       <c r="AJ2">
-        <v>0.6483720930232558</v>
+        <v>0.7063755117956717</v>
       </c>
       <c r="AK2">
-        <v>0.3681986265187533</v>
+        <v>0.4118683567327914</v>
       </c>
       <c r="AL2">
-        <v>0.309</v>
+        <v>0.399</v>
       </c>
       <c r="AM2">
-        <v>0.309</v>
+        <v>0.393</v>
       </c>
       <c r="AN2">
-        <v>-20.52631578947368</v>
+        <v>-21.6986301369863</v>
       </c>
       <c r="AO2">
-        <v>-3.17799352750809</v>
+        <v>-2.453634085213033</v>
       </c>
       <c r="AP2">
-        <v>-19.30747922437673</v>
+        <v>-19.85205479452055</v>
       </c>
       <c r="AQ2">
-        <v>-3.17799352750809</v>
+        <v>-2.491094147582698</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.008159999999999999</v>
+        <v>-0.167</v>
       </c>
       <c r="G3">
-        <v>-0.1710280373831776</v>
+        <v>-0.5579868708971554</v>
       </c>
       <c r="H3">
-        <v>-0.1710280373831776</v>
+        <v>-0.5579868708971554</v>
       </c>
       <c r="I3">
-        <v>-0.2757009345794392</v>
+        <v>-0.437636761487965</v>
       </c>
       <c r="J3">
-        <v>-0.2757009345794392</v>
+        <v>-0.437636761487965</v>
       </c>
       <c r="K3">
-        <v>-0.254</v>
+        <v>-0.452</v>
       </c>
       <c r="L3">
-        <v>-0.2373831775700934</v>
+        <v>-0.9890590809628008</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.102</v>
+        <v>0.054</v>
       </c>
       <c r="V3">
-        <v>0.04267782426778242</v>
+        <v>0.02647058823529412</v>
       </c>
       <c r="W3">
-        <v>-0.02419047619047619</v>
+        <v>-0.04388349514563106</v>
       </c>
       <c r="X3">
-        <v>0.2372037833148633</v>
+        <v>0.2067660479456278</v>
       </c>
       <c r="Y3">
-        <v>-0.2613942595053395</v>
+        <v>-0.2506495430912589</v>
       </c>
       <c r="Z3">
-        <v>0.09067028217947633</v>
+        <v>0.03934567369780456</v>
       </c>
       <c r="AA3">
-        <v>-0.0249978815354631</v>
+        <v>-0.01721911321566939</v>
       </c>
       <c r="AB3">
-        <v>0.1837237631503055</v>
+        <v>0.1504436143504277</v>
       </c>
       <c r="AC3">
-        <v>-0.2087216446857686</v>
+        <v>-0.1676627275660971</v>
       </c>
       <c r="AD3">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="AG3">
-        <v>1.278</v>
+        <v>1.626</v>
       </c>
       <c r="AH3">
-        <v>0.3660477453580901</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="AI3">
-        <v>0.1181506849315068</v>
+        <v>0.1462140992167102</v>
       </c>
       <c r="AJ3">
-        <v>0.3484187568157033</v>
+        <v>0.4435351882160393</v>
       </c>
       <c r="AK3">
-        <v>0.1103817585075142</v>
+        <v>0.1421825813221406</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-5.49800796812749</v>
+        <v>-10.12048192771084</v>
       </c>
       <c r="AP3">
-        <v>-5.091633466135457</v>
+        <v>-9.795180722891565</v>
       </c>
     </row>
     <row r="4">
@@ -838,25 +838,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.127</v>
+        <v>-0.201</v>
       </c>
       <c r="G4">
-        <v>0.1385714285714286</v>
+        <v>-0.1111650485436893</v>
       </c>
       <c r="H4">
-        <v>0.1385714285714286</v>
+        <v>-0.1111650485436893</v>
       </c>
       <c r="I4">
-        <v>-0.3271428571428572</v>
+        <v>-0.3781553398058252</v>
       </c>
       <c r="J4">
-        <v>-0.3271428571428572</v>
+        <v>-0.3781553398058252</v>
       </c>
       <c r="K4">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
       <c r="L4">
-        <v>-0.5285714285714286</v>
+        <v>-0.5436893203883496</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,73 +880,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.338</v>
+        <v>0.62</v>
       </c>
       <c r="V4">
-        <v>0.2431654676258993</v>
+        <v>0.6378600823045267</v>
       </c>
       <c r="W4">
-        <v>-0.37123745819398</v>
+        <v>-0.674698795180723</v>
       </c>
       <c r="X4">
-        <v>0.6455103424471467</v>
+        <v>0.6600876013889367</v>
       </c>
       <c r="Y4">
-        <v>-1.016747800641127</v>
+        <v>-1.33478639656966</v>
       </c>
       <c r="Z4">
-        <v>0.2445557237684873</v>
+        <v>0.280195865070729</v>
       </c>
       <c r="AA4">
-        <v>-0.08000465820426227</v>
+        <v>-0.1059575625680087</v>
       </c>
       <c r="AB4">
-        <v>0.1874840789635837</v>
+        <v>0.1540866645429759</v>
       </c>
       <c r="AC4">
-        <v>-0.2674887371678459</v>
+        <v>-0.2600442271109846</v>
       </c>
       <c r="AD4">
-        <v>6.03</v>
+        <v>6.24</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>6.03</v>
+        <v>6.24</v>
       </c>
       <c r="AG4">
-        <v>5.692</v>
+        <v>5.62</v>
       </c>
       <c r="AH4">
-        <v>0.8126684636118598</v>
+        <v>0.8652246256239601</v>
       </c>
       <c r="AI4">
-        <v>0.7841352405721717</v>
+        <v>0.9207613988490483</v>
       </c>
       <c r="AJ4">
-        <v>0.8037277605196272</v>
+        <v>0.8525485436893203</v>
       </c>
       <c r="AK4">
-        <v>0.7742110990206746</v>
+        <v>0.9127821991229496</v>
       </c>
       <c r="AL4">
-        <v>0.309</v>
+        <v>0.399</v>
       </c>
       <c r="AM4">
-        <v>0.309</v>
+        <v>0.393</v>
       </c>
       <c r="AN4">
-        <v>-54.81818181818182</v>
+        <v>-31.35678391959799</v>
       </c>
       <c r="AO4">
-        <v>-2.223300970873787</v>
+        <v>-1.952380952380952</v>
       </c>
       <c r="AP4">
-        <v>-51.74545454545455</v>
+        <v>-28.24120603015075</v>
       </c>
       <c r="AQ4">
-        <v>-2.223300970873787</v>
+        <v>-1.982188295165394</v>
       </c>
     </row>
   </sheetData>
